--- a/review/abilities/workbooks/30_Universal_Abilities.xlsx
+++ b/review/abilities/workbooks/30_Universal_Abilities.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Abilities" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Review Queue" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Action &amp; Type Audit" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Families" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Distribution" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Change Log" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Abilities" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review Queue" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Action &amp; Type Audit" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Families" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Distribution" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Change Log" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Abilities'!$A$4:$V$22</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Abilities'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Review Queue'!$A$4:$J$11</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Review Queue'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Change Log'!$A$4:$R$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Change Log'!$A$4:$Q$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'Change Log'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Change Log'!$A$1:$R$16</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Change Log'!$A$1:$Q$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -190,7 +190,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <font>
         <name val="Calibri"/>
@@ -227,19 +227,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00F8CBAD"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Calibri"/>
-        <b val="1"/>
-        <color rgb="001F3864"/>
-        <sz val="9"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00D9E1F2"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3080,15 +3067,12 @@
       <formula>T5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>T5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>T5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="T5:T22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="T5:T22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -3491,15 +3475,12 @@
       <formula>I5="Cut"</formula>
     </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>I5="Playtest"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
       <formula>I5="Unsure"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="I5:I11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut, Playtest or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
-      <formula1>"Keep,Revise,Cut,Playtest,Unsure"</formula1>
+    <dataValidation sqref="I5:I11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose Keep, Revise, Cut or Unsure." promptTitle="Decision" prompt="Your review decision for this row." type="list">
+      <formula1>"Keep,Revise,Cut,Unsure"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
@@ -4996,7 +4977,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5011,12 +4992,11 @@
     <col width="42" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="12" customWidth="1" min="15" max="15"/>
-    <col width="14" customWidth="1" min="16" max="16"/>
-    <col width="12" customWidth="1" style="11" min="17" max="17"/>
-    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" style="11" min="16" max="16"/>
+    <col width="30" customWidth="1" min="17" max="17"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -5097,30 +5077,25 @@
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>Playtest status</t>
+          <t>Book issue</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>Book issue</t>
+          <t>Foundry issue</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>Foundry issue</t>
+          <t>Commit SHA</t>
         </is>
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>Commit SHA</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -5144,7 +5119,6 @@
       <c r="O5" s="7" t="inlineStr"/>
       <c r="P5" s="7" t="inlineStr"/>
       <c r="Q5" s="7" t="inlineStr"/>
-      <c r="R5" s="7" t="inlineStr"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
       <c r="A6" s="9" t="inlineStr"/>
@@ -5164,7 +5138,6 @@
       <c r="O6" s="9" t="inlineStr"/>
       <c r="P6" s="9" t="inlineStr"/>
       <c r="Q6" s="9" t="inlineStr"/>
-      <c r="R6" s="9" t="inlineStr"/>
     </row>
     <row r="7" ht="16.5" customHeight="1">
       <c r="A7" s="7" t="inlineStr"/>
@@ -5184,7 +5157,6 @@
       <c r="O7" s="7" t="inlineStr"/>
       <c r="P7" s="7" t="inlineStr"/>
       <c r="Q7" s="7" t="inlineStr"/>
-      <c r="R7" s="7" t="inlineStr"/>
     </row>
     <row r="8" ht="16.5" customHeight="1">
       <c r="A8" s="9" t="inlineStr"/>
@@ -5204,7 +5176,6 @@
       <c r="O8" s="9" t="inlineStr"/>
       <c r="P8" s="9" t="inlineStr"/>
       <c r="Q8" s="9" t="inlineStr"/>
-      <c r="R8" s="9" t="inlineStr"/>
     </row>
     <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="7" t="inlineStr"/>
@@ -5224,7 +5195,6 @@
       <c r="O9" s="7" t="inlineStr"/>
       <c r="P9" s="7" t="inlineStr"/>
       <c r="Q9" s="7" t="inlineStr"/>
-      <c r="R9" s="7" t="inlineStr"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="9" t="inlineStr"/>
@@ -5244,7 +5214,6 @@
       <c r="O10" s="9" t="inlineStr"/>
       <c r="P10" s="9" t="inlineStr"/>
       <c r="Q10" s="9" t="inlineStr"/>
-      <c r="R10" s="9" t="inlineStr"/>
     </row>
     <row r="11" ht="16.5" customHeight="1">
       <c r="A11" s="7" t="inlineStr"/>
@@ -5264,7 +5233,6 @@
       <c r="O11" s="7" t="inlineStr"/>
       <c r="P11" s="7" t="inlineStr"/>
       <c r="Q11" s="7" t="inlineStr"/>
-      <c r="R11" s="7" t="inlineStr"/>
     </row>
     <row r="12" ht="16.5" customHeight="1">
       <c r="A12" s="9" t="inlineStr"/>
@@ -5284,7 +5252,6 @@
       <c r="O12" s="9" t="inlineStr"/>
       <c r="P12" s="9" t="inlineStr"/>
       <c r="Q12" s="9" t="inlineStr"/>
-      <c r="R12" s="9" t="inlineStr"/>
     </row>
     <row r="13" ht="16.5" customHeight="1">
       <c r="A13" s="7" t="inlineStr"/>
@@ -5304,7 +5271,6 @@
       <c r="O13" s="7" t="inlineStr"/>
       <c r="P13" s="7" t="inlineStr"/>
       <c r="Q13" s="7" t="inlineStr"/>
-      <c r="R13" s="7" t="inlineStr"/>
     </row>
     <row r="14" ht="16.5" customHeight="1">
       <c r="A14" s="9" t="inlineStr"/>
@@ -5324,7 +5290,6 @@
       <c r="O14" s="9" t="inlineStr"/>
       <c r="P14" s="9" t="inlineStr"/>
       <c r="Q14" s="9" t="inlineStr"/>
-      <c r="R14" s="9" t="inlineStr"/>
     </row>
     <row r="15" ht="16.5" customHeight="1">
       <c r="A15" s="7" t="inlineStr"/>
@@ -5344,7 +5309,6 @@
       <c r="O15" s="7" t="inlineStr"/>
       <c r="P15" s="7" t="inlineStr"/>
       <c r="Q15" s="7" t="inlineStr"/>
-      <c r="R15" s="7" t="inlineStr"/>
     </row>
     <row r="16" ht="16.5" customHeight="1">
       <c r="A16" s="9" t="inlineStr"/>
@@ -5364,23 +5328,19 @@
       <c r="O16" s="9" t="inlineStr"/>
       <c r="P16" s="9" t="inlineStr"/>
       <c r="Q16" s="9" t="inlineStr"/>
-      <c r="R16" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:R204"/>
+  <autoFilter ref="A4:Q204"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:R2"/>
-    <mergeCell ref="A1:R1"/>
+    <mergeCell ref="A2:Q2"/>
+    <mergeCell ref="A1:Q1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="2">
     <dataValidation sqref="I5:I204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Change type" error="Choose one of: Editorial, Wording, Mechanical, Rename, Add, Remove, Tier / DP, ID migration" promptTitle="Change type" prompt="Classify the change." type="list">
       <formula1>"Editorial,Wording,Mechanical,Rename,Add,Remove,Tier / DP,ID migration"</formula1>
     </dataValidation>
     <dataValidation sqref="K5:K204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Decision" error="Choose one of: Proposed, Approved, Rejected, Deferred" promptTitle="Decision" prompt="Approval state for this change." type="list">
       <formula1>"Proposed,Approved,Rejected,Deferred"</formula1>
-    </dataValidation>
-    <dataValidation sqref="M5:M204" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Playtest status" error="Choose one of: Not needed, Pending, Passed, Failed, N/A" promptTitle="Playtest status" prompt="Playtest evidence for mechanical changes." type="list">
-      <formula1>"Not needed,Pending,Passed,Failed,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="1"/>
